--- a/output/第10期計画_見える化システムからご出力をお願いする資料.xlsx
+++ b/output/第10期計画_見える化システムからご出力をお願いする資料.xlsx
@@ -846,7 +846,7 @@
         <is>
           <t>本資料の画面の順路及び出力の形式は、公表されている「地域包括ケア「見える化」システム等を活用した地域分析の手引き（令和8年9月改訂版）」、「第10期介護保険事業（支援）計画に向けた現在及び中長期的な地域分析と新機能」及び同システムのお知らせにより確かめたものです（令和8年10月23日）。
 画面の名称がシステムの表示と異なる場合はシステムの表示によってください。
-基準日：令和8年10月23日</t>
+基準日：令和8年10月24日</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>資料提供依頼No.25（事業所分析機能）が台帳にあり未受領であること</t>
+          <t>資料提供依頼No.25（事業所分析機能）が台帳にあること</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>受領済</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>自己点検 26件　不適合 0件　基準日 令和8年10月23日</t>
+          <t>自己点検 26件　不適合 0件　基準日 令和8年10月24日</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>解決</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>解決</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>受領済</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>受領済</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
